--- a/out/thesis/tables/one_sample_tests.xlsx
+++ b/out/thesis/tables/one_sample_tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>metric</t>
   </si>
@@ -55,6 +55,9 @@
     <t>CAR_ANN_NEXT_DAY</t>
   </si>
   <si>
+    <t>ratio_1h_vs_day</t>
+  </si>
+  <si>
     <t>CAR_ANN_1_1</t>
   </si>
   <si>
@@ -70,12 +73,6 @@
     <t>BHAR_ANN_60</t>
   </si>
   <si>
-    <t>BHAR_ANN_120</t>
-  </si>
-  <si>
-    <t>BHAR_ANN_250</t>
-  </si>
-  <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
@@ -92,9 +89,6 @@
   </si>
   <si>
     <t>BHAR_CLOSE_120</t>
-  </si>
-  <si>
-    <t>BHAR_CLOSE_250</t>
   </si>
   <si>
     <t>RUNUP_PRE_30_5</t>
@@ -444,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -472,13 +466,13 @@
         <v>61</v>
       </c>
       <c r="C2">
-        <v>0.002091472032654441</v>
+        <v>0.001199727994858157</v>
       </c>
       <c r="D2">
-        <v>1.529767234976306</v>
+        <v>1.52459520650106</v>
       </c>
       <c r="E2">
-        <v>0.13132986580881</v>
+        <v>0.1326141402864481</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -489,13 +483,13 @@
         <v>61</v>
       </c>
       <c r="C3">
-        <v>0.0007960819640465093</v>
+        <v>-9.566207374977578E-05</v>
       </c>
       <c r="D3">
-        <v>0.6313040409456865</v>
+        <v>-0.101251197914202</v>
       </c>
       <c r="E3">
-        <v>0.5302395311545847</v>
+        <v>0.9196886549119869</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -540,13 +534,13 @@
         <v>61</v>
       </c>
       <c r="C6">
-        <v>0.00483168657668591</v>
+        <v>0.004379907928898975</v>
       </c>
       <c r="D6">
-        <v>0.8267273460350543</v>
+        <v>0.7614743087744736</v>
       </c>
       <c r="E6">
-        <v>0.4116673439029424</v>
+        <v>0.4493565211056466</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -605,16 +599,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="C10">
-        <v>0.0004031446113741195</v>
+        <v>17.96630035866757</v>
       </c>
       <c r="D10">
-        <v>0.1246562992421421</v>
+        <v>1.152896244919047</v>
       </c>
       <c r="E10">
-        <v>0.9009975145171599</v>
+        <v>0.2535254248826208</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -625,13 +619,13 @@
         <v>125</v>
       </c>
       <c r="C11">
-        <v>-0.001243392319941792</v>
+        <v>0.0003562432390699621</v>
       </c>
       <c r="D11">
-        <v>-0.2519727596513911</v>
+        <v>0.1104651322697253</v>
       </c>
       <c r="E11">
-        <v>0.8014792722212764</v>
+        <v>0.9122190902304981</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -642,13 +636,13 @@
         <v>125</v>
       </c>
       <c r="C12">
-        <v>0.005285064335128388</v>
+        <v>-0.001515966472595225</v>
       </c>
       <c r="D12">
-        <v>0.8650519342406952</v>
+        <v>-0.3092932917410041</v>
       </c>
       <c r="E12">
-        <v>0.388680752457183</v>
+        <v>0.7576175405400369</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -659,13 +653,13 @@
         <v>125</v>
       </c>
       <c r="C13">
-        <v>0.01133121375920442</v>
+        <v>0.005570799893693436</v>
       </c>
       <c r="D13">
-        <v>1.403340511595824</v>
+        <v>0.9088717685285568</v>
       </c>
       <c r="E13">
-        <v>0.1630145171498954</v>
+        <v>0.3651809311742531</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -673,16 +667,16 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C14">
-        <v>0.05552097327060793</v>
+        <v>0.01141388919032527</v>
       </c>
       <c r="D14">
-        <v>3.715518275962508</v>
+        <v>1.410327195713072</v>
       </c>
       <c r="E14">
-        <v>0.0002936903076566731</v>
+        <v>0.1609466726152891</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -690,16 +684,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>137</v>
+        <v>30</v>
       </c>
       <c r="C15">
-        <v>0.08295627658393388</v>
+        <v>0.09753266661330695</v>
       </c>
       <c r="D15">
-        <v>3.923145439396067</v>
+        <v>2.294038891323789</v>
       </c>
       <c r="E15">
-        <v>0.0001381114002058026</v>
+        <v>0.02922145898347224</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -707,16 +701,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="C16">
-        <v>0.04452940841308847</v>
+        <v>-0.0009259959478472051</v>
       </c>
       <c r="D16">
-        <v>1.397337781926339</v>
+        <v>-0.3036093195627279</v>
       </c>
       <c r="E16">
-        <v>0.1648275305446935</v>
+        <v>0.762089489205738</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -724,16 +718,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C17">
-        <v>0.0004905706210143237</v>
+        <v>0.00238139979255795</v>
       </c>
       <c r="D17">
-        <v>0.1585972671878249</v>
+        <v>0.4161398600121091</v>
       </c>
       <c r="E17">
-        <v>0.8743125483953407</v>
+        <v>0.6782462788773366</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -741,16 +735,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C18">
-        <v>0.004446452537794658</v>
+        <v>0.01140953665531187</v>
       </c>
       <c r="D18">
-        <v>0.7801345083010168</v>
+        <v>1.74924315176968</v>
       </c>
       <c r="E18">
-        <v>0.4371918796217897</v>
+        <v>0.08347857365240649</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -758,16 +752,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C19">
-        <v>0.01301030067761407</v>
+        <v>0.004984469649769689</v>
       </c>
       <c r="D19">
-        <v>2.011560839305521</v>
+        <v>0.4687313687079792</v>
       </c>
       <c r="E19">
-        <v>0.04701194103505182</v>
+        <v>0.640346890432827</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -775,16 +769,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="C20">
-        <v>0.006266923758522714</v>
+        <v>0.02444790427551347</v>
       </c>
       <c r="D20">
-        <v>0.6082157049087487</v>
+        <v>0.6175519943763819</v>
       </c>
       <c r="E20">
-        <v>0.544451478836384</v>
+        <v>0.5455603884543609</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -792,16 +786,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="C21">
-        <v>0.04724645054018276</v>
+        <v>0.144464350765866</v>
       </c>
       <c r="D21">
-        <v>3.399512657345882</v>
+        <v>2.123759605972077</v>
       </c>
       <c r="E21">
-        <v>0.0009846787910216259</v>
+        <v>0.08708975020600319</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -809,16 +803,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C22">
-        <v>0.07340772866018906</v>
+        <v>0.01807559469166843</v>
       </c>
       <c r="D22">
-        <v>3.090594577730312</v>
+        <v>2.089307232457232</v>
       </c>
       <c r="E22">
-        <v>0.002650542871823653</v>
+        <v>0.03874120508725593</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -826,16 +820,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="C23">
-        <v>0.004000556722088157</v>
+        <v>0.02294005261910105</v>
       </c>
       <c r="D23">
-        <v>0.09653341328725566</v>
+        <v>2.629098025538805</v>
       </c>
       <c r="E23">
-        <v>0.9233614697504724</v>
+        <v>0.009653393433829954</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -846,13 +840,13 @@
         <v>124</v>
       </c>
       <c r="C24">
-        <v>0.01816274659278014</v>
+        <v>0.002173359413271701</v>
       </c>
       <c r="D24">
-        <v>2.09541918631014</v>
+        <v>0.6484988129900904</v>
       </c>
       <c r="E24">
-        <v>0.03818465332446676</v>
+        <v>0.5178712560525042</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -863,13 +857,13 @@
         <v>124</v>
       </c>
       <c r="C25">
-        <v>0.02289898046432037</v>
+        <v>0.003197199375058779</v>
       </c>
       <c r="D25">
-        <v>2.625738560515452</v>
+        <v>0.6586185577923472</v>
       </c>
       <c r="E25">
-        <v>0.009743964302391887</v>
+        <v>0.5113717294517035</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -877,16 +871,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C26">
-        <v>0.002172341655948481</v>
+        <v>-0.001199623914782526</v>
       </c>
       <c r="D26">
-        <v>0.6481931492710465</v>
+        <v>-0.3426063130507623</v>
       </c>
       <c r="E26">
-        <v>0.518068243088123</v>
+        <v>0.7324700875646861</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -894,50 +888,16 @@
         <v>30</v>
       </c>
       <c r="B27">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C27">
-        <v>0.003194690470211211</v>
+        <v>-0.001429053484884809</v>
       </c>
       <c r="D27">
-        <v>0.6581480924506373</v>
+        <v>-0.2524623454117265</v>
       </c>
       <c r="E27">
-        <v>0.5116729329686149</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28">
-        <v>126</v>
-      </c>
-      <c r="C28">
-        <v>-0.001213900410916014</v>
-      </c>
-      <c r="D28">
-        <v>-0.3466481436084926</v>
-      </c>
-      <c r="E28">
-        <v>0.7294385342036267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29">
-        <v>126</v>
-      </c>
-      <c r="C29">
-        <v>-0.001460098561881292</v>
-      </c>
-      <c r="D29">
-        <v>-0.2579217423975697</v>
-      </c>
-      <c r="E29">
-        <v>0.7968914571644596</v>
+        <v>0.8010983839765703</v>
       </c>
     </row>
   </sheetData>

--- a/out/thesis/tables/one_sample_tests.xlsx
+++ b/out/thesis/tables/one_sample_tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>metric</t>
   </si>
@@ -37,6 +37,9 @@
     <t>CAR_ANN_INTRADAY_30M</t>
   </si>
   <si>
+    <t>CAR_ANN_INTRADAY_M60_P180</t>
+  </si>
+  <si>
     <t>CAR_ANN_INTRADAY_1H</t>
   </si>
   <si>
@@ -70,9 +73,6 @@
     <t>CAR_ANN_10_10</t>
   </si>
   <si>
-    <t>BHAR_ANN_60</t>
-  </si>
-  <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
@@ -86,9 +86,6 @@
   </si>
   <si>
     <t>BHAR_CLOSE_60</t>
-  </si>
-  <si>
-    <t>BHAR_CLOSE_120</t>
   </si>
   <si>
     <t>RUNUP_PRE_30_5</t>
@@ -438,7 +435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -463,16 +460,16 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C2">
-        <v>0.001199727994858157</v>
+        <v>-0.002078193354837277</v>
       </c>
       <c r="D2">
-        <v>1.52459520650106</v>
+        <v>-0.8580568122926181</v>
       </c>
       <c r="E2">
-        <v>0.1326141402864481</v>
+        <v>0.3941660988137266</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -480,16 +477,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C3">
-        <v>-9.566207374977578E-05</v>
+        <v>-0.003417212874368534</v>
       </c>
       <c r="D3">
-        <v>-0.101251197914202</v>
+        <v>-1.365378214622428</v>
       </c>
       <c r="E3">
-        <v>0.9196886549119869</v>
+        <v>0.1770678734178362</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -497,16 +494,16 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>0.0004584012071024731</v>
+        <v>-0.003231069893909831</v>
       </c>
       <c r="D4">
-        <v>0.4898290057280546</v>
+        <v>-0.8198605459731844</v>
       </c>
       <c r="E4">
-        <v>0.6260411627344658</v>
+        <v>0.4154363696062995</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -514,16 +511,16 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>0.0003559423720667383</v>
+        <v>-0.003403930815966738</v>
       </c>
       <c r="D5">
-        <v>0.1987723279749866</v>
+        <v>-1.191677038397429</v>
       </c>
       <c r="E5">
-        <v>0.8431128658716438</v>
+        <v>0.2379296023189033</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -531,16 +528,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6">
-        <v>0.004379907928898975</v>
+        <v>-0.004387107744967301</v>
       </c>
       <c r="D6">
-        <v>0.7614743087744736</v>
+        <v>-1.169520968968914</v>
       </c>
       <c r="E6">
-        <v>0.4493565211056466</v>
+        <v>0.2466703163707958</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -548,16 +545,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>0.002193531755543433</v>
+        <v>0.0002700488514069686</v>
       </c>
       <c r="D7">
-        <v>0.6737190803878608</v>
+        <v>0.04307173158939862</v>
       </c>
       <c r="E7">
-        <v>0.5030771316177108</v>
+        <v>0.9657827697392729</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -565,16 +562,16 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8">
-        <v>-0.0008937873069912753</v>
+        <v>-0.002607854532394627</v>
       </c>
       <c r="D8">
-        <v>-0.9514217146216999</v>
+        <v>-0.5654077529995143</v>
       </c>
       <c r="E8">
-        <v>0.3452073588680343</v>
+        <v>0.5738369373275802</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -582,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>0.002120267944568103</v>
+        <v>-0.0001976817575056889</v>
       </c>
       <c r="D9">
-        <v>0.7049679148584954</v>
+        <v>-0.1915265408454373</v>
       </c>
       <c r="E9">
-        <v>0.4835579456051755</v>
+        <v>0.8487389538723461</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -599,16 +596,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C10">
-        <v>17.96630035866757</v>
+        <v>0.002813893828943917</v>
       </c>
       <c r="D10">
-        <v>1.152896244919047</v>
+        <v>0.9533042469782642</v>
       </c>
       <c r="E10">
-        <v>0.2535254248826208</v>
+        <v>0.3441379253739614</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -616,16 +613,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="C11">
-        <v>0.0003562432390699621</v>
+        <v>19.97747538752922</v>
       </c>
       <c r="D11">
-        <v>0.1104651322697253</v>
+        <v>1.318582220203645</v>
       </c>
       <c r="E11">
-        <v>0.9122190902304981</v>
+        <v>0.1921590050981655</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -636,13 +633,13 @@
         <v>125</v>
       </c>
       <c r="C12">
-        <v>-0.001515966472595225</v>
+        <v>0.0003562432390699621</v>
       </c>
       <c r="D12">
-        <v>-0.3092932917410041</v>
+        <v>0.1104651322697253</v>
       </c>
       <c r="E12">
-        <v>0.7576175405400369</v>
+        <v>0.9122190902304981</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -653,13 +650,13 @@
         <v>125</v>
       </c>
       <c r="C13">
-        <v>0.005570799893693436</v>
+        <v>-0.001515966472595225</v>
       </c>
       <c r="D13">
-        <v>0.9088717685285568</v>
+        <v>-0.3092932917410041</v>
       </c>
       <c r="E13">
-        <v>0.3651809311742531</v>
+        <v>0.7576175405400369</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -670,13 +667,13 @@
         <v>125</v>
       </c>
       <c r="C14">
-        <v>0.01141388919032527</v>
+        <v>0.005570799893693436</v>
       </c>
       <c r="D14">
-        <v>1.410327195713072</v>
+        <v>0.9088717685285568</v>
       </c>
       <c r="E14">
-        <v>0.1609466726152891</v>
+        <v>0.3651809311742531</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -684,16 +681,16 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="C15">
-        <v>0.09753266661330695</v>
+        <v>0.01102386544064671</v>
       </c>
       <c r="D15">
-        <v>2.294038891323789</v>
+        <v>1.361325453608925</v>
       </c>
       <c r="E15">
-        <v>0.02922145898347224</v>
+        <v>0.1758794678685959</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -701,16 +698,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C16">
-        <v>-0.0009259959478472051</v>
+        <v>-0.0006033777277797611</v>
       </c>
       <c r="D16">
-        <v>-0.3036093195627279</v>
+        <v>-0.1731952510823132</v>
       </c>
       <c r="E16">
-        <v>0.762089489205738</v>
+        <v>0.8628480438918376</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -718,16 +715,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C17">
-        <v>0.00238139979255795</v>
+        <v>0.003239123481441927</v>
       </c>
       <c r="D17">
-        <v>0.4161398600121091</v>
+        <v>0.5634350976974515</v>
       </c>
       <c r="E17">
-        <v>0.6782462788773366</v>
+        <v>0.5743999079006592</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -735,16 +732,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C18">
-        <v>0.01140953665531187</v>
+        <v>0.01104106361583274</v>
       </c>
       <c r="D18">
-        <v>1.74924315176968</v>
+        <v>1.684725384455997</v>
       </c>
       <c r="E18">
-        <v>0.08347857365240649</v>
+        <v>0.0951601870232593</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -752,16 +749,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="C19">
-        <v>0.004984469649769689</v>
+        <v>0.005065025401463818</v>
       </c>
       <c r="D19">
-        <v>0.4687313687079792</v>
+        <v>0.4886023158561802</v>
       </c>
       <c r="E19">
-        <v>0.640346890432827</v>
+        <v>0.6262148695508324</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -769,16 +766,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C20">
-        <v>0.02444790427551347</v>
+        <v>0.09964812691641563</v>
       </c>
       <c r="D20">
-        <v>0.6175519943763819</v>
+        <v>1.594743915862403</v>
       </c>
       <c r="E20">
-        <v>0.5455603884543609</v>
+        <v>0.1716535300899578</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -786,16 +783,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>124</v>
       </c>
       <c r="C21">
-        <v>0.144464350765866</v>
+        <v>0.01807559469166843</v>
       </c>
       <c r="D21">
-        <v>2.123759605972077</v>
+        <v>2.089307232457232</v>
       </c>
       <c r="E21">
-        <v>0.08708975020600319</v>
+        <v>0.03874120508725593</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -806,13 +803,13 @@
         <v>124</v>
       </c>
       <c r="C22">
-        <v>0.01807559469166843</v>
+        <v>0.02294005261910105</v>
       </c>
       <c r="D22">
-        <v>2.089307232457232</v>
+        <v>2.629098025538805</v>
       </c>
       <c r="E22">
-        <v>0.03874120508725593</v>
+        <v>0.009653393433829954</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -823,13 +820,13 @@
         <v>124</v>
       </c>
       <c r="C23">
-        <v>0.02294005261910105</v>
+        <v>0.002173359413271701</v>
       </c>
       <c r="D23">
-        <v>2.629098025538805</v>
+        <v>0.6484988129900904</v>
       </c>
       <c r="E23">
-        <v>0.009653393433829954</v>
+        <v>0.5178712560525042</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -840,13 +837,13 @@
         <v>124</v>
       </c>
       <c r="C24">
-        <v>0.002173359413271701</v>
+        <v>0.003197199375058779</v>
       </c>
       <c r="D24">
-        <v>0.6484988129900904</v>
+        <v>0.6586185577923472</v>
       </c>
       <c r="E24">
-        <v>0.5178712560525042</v>
+        <v>0.5113717294517035</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -857,13 +854,13 @@
         <v>124</v>
       </c>
       <c r="C25">
-        <v>0.003197199375058779</v>
+        <v>-0.000506522846464162</v>
       </c>
       <c r="D25">
-        <v>0.6586185577923472</v>
+        <v>-0.1481958924256929</v>
       </c>
       <c r="E25">
-        <v>0.5113717294517035</v>
+        <v>0.8824308478683043</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -871,33 +868,16 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26">
-        <v>-0.001199623914782526</v>
+        <v>0.003976883696962459</v>
       </c>
       <c r="D26">
-        <v>-0.3426063130507623</v>
+        <v>0.7647882829696149</v>
       </c>
       <c r="E26">
-        <v>0.7324700875646861</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27">
-        <v>126</v>
-      </c>
-      <c r="C27">
-        <v>-0.001429053484884809</v>
-      </c>
-      <c r="D27">
-        <v>-0.2524623454117265</v>
-      </c>
-      <c r="E27">
-        <v>0.8010983839765703</v>
+        <v>0.4458624623936648</v>
       </c>
     </row>
   </sheetData>

--- a/out/thesis/tables/one_sample_tests.xlsx
+++ b/out/thesis/tables/one_sample_tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t>metric</t>
   </si>
@@ -73,6 +73,24 @@
     <t>CAR_ANN_10_10</t>
   </si>
   <si>
+    <t>CAR_ANN_30_30</t>
+  </si>
+  <si>
+    <t>CAR_ANN_50_50</t>
+  </si>
+  <si>
+    <t>CAR_ANN_30_5</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_60</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_120</t>
+  </si>
+  <si>
+    <t>BHAR_ANN_250</t>
+  </si>
+  <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
@@ -88,22 +106,55 @@
     <t>BHAR_CLOSE_60</t>
   </si>
   <si>
+    <t>BHAR_CLOSE_120</t>
+  </si>
+  <si>
+    <t>BHAR_CLOSE_250</t>
+  </si>
+  <si>
     <t>RUNUP_PRE_30_5</t>
   </si>
   <si>
     <t>CAR_PRE_ANNOUNCEMENT</t>
   </si>
   <si>
+    <t>DIFF_CAR_ANN_MINUS_CREATE_1_1</t>
+  </si>
+  <si>
     <t>CAR_CREATE_1_1</t>
   </si>
   <si>
     <t>CAR_CREATE_3_3</t>
   </si>
   <si>
+    <t>CAR_CREATE_30_5</t>
+  </si>
+  <si>
+    <t>CAR_ACT_30_30</t>
+  </si>
+  <si>
+    <t>CAR_ACT_50_50</t>
+  </si>
+  <si>
+    <t>CAR_ACT_30_5</t>
+  </si>
+  <si>
+    <t>CAR_CREATE_30_30</t>
+  </si>
+  <si>
+    <t>CAR_CREATE_50_50</t>
+  </si>
+  <si>
     <t>CAR_ACT_1_1</t>
   </si>
   <si>
     <t>CAR_ACT_3_3</t>
+  </si>
+  <si>
+    <t>DIFF_CAR_ANN_CREATE_1_1</t>
+  </si>
+  <si>
+    <t>DIFF_CAR_ANN_CREATE_30_5</t>
   </si>
 </sst>
 </file>
@@ -435,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -684,13 +735,13 @@
         <v>125</v>
       </c>
       <c r="C15">
-        <v>0.01102386544064671</v>
+        <v>0.01141388919032527</v>
       </c>
       <c r="D15">
-        <v>1.361325453608925</v>
+        <v>1.410327195713072</v>
       </c>
       <c r="E15">
-        <v>0.1758794678685959</v>
+        <v>0.1609466726152891</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -698,16 +749,16 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C16">
-        <v>-0.0006033777277797611</v>
+        <v>0.03840210554338377</v>
       </c>
       <c r="D16">
-        <v>-0.1731952510823132</v>
+        <v>2.904095589207998</v>
       </c>
       <c r="E16">
-        <v>0.8628480438918376</v>
+        <v>0.004367596166801536</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -715,16 +766,16 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C17">
-        <v>0.003239123481441927</v>
+        <v>0.05894287004584058</v>
       </c>
       <c r="D17">
-        <v>0.5634350976974515</v>
+        <v>3.043233359033138</v>
       </c>
       <c r="E17">
-        <v>0.5743999079006592</v>
+        <v>0.002862390633184217</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -732,16 +783,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="C18">
-        <v>0.01104106361583274</v>
+        <v>0.01807559469166843</v>
       </c>
       <c r="D18">
-        <v>1.684725384455997</v>
+        <v>2.089307232457232</v>
       </c>
       <c r="E18">
-        <v>0.0951601870232593</v>
+        <v>0.03874120508725593</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -749,16 +800,16 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>0.005065025401463818</v>
+        <v>0.02938113122092688</v>
       </c>
       <c r="D19">
-        <v>0.4886023158561802</v>
+        <v>0.7689815389760443</v>
       </c>
       <c r="E19">
-        <v>0.6262148695508324</v>
+        <v>0.4494061779246257</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -766,16 +817,16 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>0.09964812691641563</v>
+        <v>0.04681414714363292</v>
       </c>
       <c r="D20">
-        <v>1.594743915862403</v>
+        <v>1.444278772676074</v>
       </c>
       <c r="E20">
-        <v>0.1716535300899578</v>
+        <v>0.1621461462177212</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -783,16 +834,16 @@
         <v>24</v>
       </c>
       <c r="B21">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="C21">
-        <v>0.01807559469166843</v>
+        <v>0.09822753841660853</v>
       </c>
       <c r="D21">
-        <v>2.089307232457232</v>
+        <v>2.094026058227822</v>
       </c>
       <c r="E21">
-        <v>0.03874120508725593</v>
+        <v>0.04920166706063821</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -800,16 +851,16 @@
         <v>25</v>
       </c>
       <c r="B22">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C22">
-        <v>0.02294005261910105</v>
+        <v>-0.0006033777277797611</v>
       </c>
       <c r="D22">
-        <v>2.629098025538805</v>
+        <v>-0.1731952510823132</v>
       </c>
       <c r="E22">
-        <v>0.009653393433829954</v>
+        <v>0.8628480438918376</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -817,16 +868,16 @@
         <v>26</v>
       </c>
       <c r="B23">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C23">
-        <v>0.002173359413271701</v>
+        <v>0.003239123481441927</v>
       </c>
       <c r="D23">
-        <v>0.6484988129900904</v>
+        <v>0.5634350976974515</v>
       </c>
       <c r="E23">
-        <v>0.5178712560525042</v>
+        <v>0.5743999079006592</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -834,16 +885,16 @@
         <v>27</v>
       </c>
       <c r="B24">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C24">
-        <v>0.003197199375058779</v>
+        <v>0.01117910734539273</v>
       </c>
       <c r="D24">
-        <v>0.6586185577923472</v>
+        <v>1.709946320407091</v>
       </c>
       <c r="E24">
-        <v>0.5113717294517035</v>
+        <v>0.09037695693694615</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -851,16 +902,16 @@
         <v>28</v>
       </c>
       <c r="B25">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="C25">
-        <v>-0.000506522846464162</v>
+        <v>0.002787607160732627</v>
       </c>
       <c r="D25">
-        <v>-0.1481958924256929</v>
+        <v>0.265571664745563</v>
       </c>
       <c r="E25">
-        <v>0.8824308478683043</v>
+        <v>0.7911158313814984</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -868,16 +919,305 @@
         <v>29</v>
       </c>
       <c r="B26">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C26">
+        <v>0.02906863230679001</v>
+      </c>
+      <c r="D26">
+        <v>0.7739012853741901</v>
+      </c>
+      <c r="E26">
+        <v>0.449618343263717</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>0.08327223382481209</v>
+      </c>
+      <c r="D27">
+        <v>2.189602580862466</v>
+      </c>
+      <c r="E27">
+        <v>0.04598730493543415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28">
+        <v>12</v>
+      </c>
+      <c r="C28">
+        <v>0.1070447241933858</v>
+      </c>
+      <c r="D28">
+        <v>1.834630840761309</v>
+      </c>
+      <c r="E28">
+        <v>0.09372544531753906</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>124</v>
+      </c>
+      <c r="C29">
+        <v>0.01807559469166843</v>
+      </c>
+      <c r="D29">
+        <v>2.089307232457232</v>
+      </c>
+      <c r="E29">
+        <v>0.03874120508725593</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30">
+        <v>124</v>
+      </c>
+      <c r="C30">
+        <v>0.02294005261910105</v>
+      </c>
+      <c r="D30">
+        <v>2.629098025538805</v>
+      </c>
+      <c r="E30">
+        <v>0.009653393433829954</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31">
+        <v>124</v>
+      </c>
+      <c r="C31">
+        <v>-0.001843891212568493</v>
+      </c>
+      <c r="D31">
+        <v>-0.6640225267937503</v>
+      </c>
+      <c r="E31">
+        <v>0.5079187070793545</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32">
+        <v>124</v>
+      </c>
+      <c r="C32">
+        <v>0.002173359413271701</v>
+      </c>
+      <c r="D32">
+        <v>0.6484988129900904</v>
+      </c>
+      <c r="E32">
+        <v>0.5178712560525042</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33">
+        <v>124</v>
+      </c>
+      <c r="C33">
+        <v>0.003197199375058779</v>
+      </c>
+      <c r="D33">
+        <v>0.6586185577923472</v>
+      </c>
+      <c r="E33">
+        <v>0.5113717294517035</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34">
+        <v>123</v>
+      </c>
+      <c r="C34">
+        <v>0.01517675200557212</v>
+      </c>
+      <c r="D34">
+        <v>1.867592358936478</v>
+      </c>
+      <c r="E34">
+        <v>0.06421853358993719</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35">
+        <v>124</v>
+      </c>
+      <c r="C35">
+        <v>0.03313518239140669</v>
+      </c>
+      <c r="D35">
+        <v>2.507123748024197</v>
+      </c>
+      <c r="E35">
+        <v>0.01347568076800288</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36">
+        <v>124</v>
+      </c>
+      <c r="C36">
+        <v>0.06310926996856751</v>
+      </c>
+      <c r="D36">
+        <v>3.935000102791771</v>
+      </c>
+      <c r="E36">
+        <v>0.0001382541929022895</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37">
+        <v>124</v>
+      </c>
+      <c r="C37">
+        <v>0.006534547239817555</v>
+      </c>
+      <c r="D37">
+        <v>0.7941224362456867</v>
+      </c>
+      <c r="E37">
+        <v>0.4286536131012592</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38">
+        <v>123</v>
+      </c>
+      <c r="C38">
+        <v>0.04121771303062292</v>
+      </c>
+      <c r="D38">
+        <v>3.508680766945595</v>
+      </c>
+      <c r="E38">
+        <v>0.0006314224246854005</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39">
+        <v>123</v>
+      </c>
+      <c r="C39">
+        <v>0.05335605611127209</v>
+      </c>
+      <c r="D39">
+        <v>2.939611221744416</v>
+      </c>
+      <c r="E39">
+        <v>0.003931786142350865</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40">
+        <v>124</v>
+      </c>
+      <c r="C40">
+        <v>-0.000506522846464162</v>
+      </c>
+      <c r="D40">
+        <v>-0.1481958924256929</v>
+      </c>
+      <c r="E40">
+        <v>0.8824308478683043</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41">
+        <v>124</v>
+      </c>
+      <c r="C41">
         <v>0.003976883696962459</v>
       </c>
-      <c r="D26">
+      <c r="D41">
         <v>0.7647882829696149</v>
       </c>
-      <c r="E26">
+      <c r="E41">
         <v>0.4458624623936648</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42">
+        <v>124</v>
+      </c>
+      <c r="C42">
+        <v>-0.001843891212568493</v>
+      </c>
+      <c r="D42">
+        <v>-0.6640225267937503</v>
+      </c>
+      <c r="E42">
+        <v>0.5079187070793545</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43">
+        <v>123</v>
+      </c>
+      <c r="C43">
+        <v>0.003172771307932802</v>
+      </c>
+      <c r="D43">
+        <v>0.5231516932639064</v>
+      </c>
+      <c r="E43">
+        <v>0.6018175800662435</v>
       </c>
     </row>
   </sheetData>
